--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,6 +1430,1930 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128774967</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105651</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626203</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6650513</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128774950</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626128</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6650581</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128774970</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6650628</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128774956</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626194</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6650588</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128774953</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626068</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6650516</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128774960</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97462</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626202</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6650484</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128774965</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6650513</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128774955</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626185</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6650516</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128774961</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97462</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626179</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6650372</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128774969</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>626079</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6650518</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128774968</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105651</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626195</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6650509</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128774958</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626230</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6650616</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128774954</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626121</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6650538</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128774952</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626218</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6650628</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128774959</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626196</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6650578</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128774963</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>626154</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6650405</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128774957</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626247</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6650626</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128774949</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626135</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6650578</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128774962</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626149</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6650411</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,46 +2037,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2084,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R14" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,6 +2111,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,37 +2143,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R15" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,11 +2226,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2447,46 +2447,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B18" t="n">
-        <v>105651</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2494,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R18" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,6 +2521,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774958</v>
+        <v>128774954</v>
       </c>
       <c r="B19" t="n">
-        <v>91466</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,34 +2564,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626230</v>
+        <v>626121</v>
       </c>
       <c r="R19" t="n">
-        <v>6650616</v>
+        <v>6650538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,12 +2629,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2654,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774954</v>
+        <v>128774958</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>91467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,37 +2670,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626121</v>
+        <v>626230</v>
       </c>
       <c r="R20" t="n">
-        <v>6650538</v>
+        <v>6650616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,18 +2732,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2760,37 +2756,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>79708</v>
+        <v>105654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>92748</v>
+        <v>79708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774957</v>
+        <v>128774962</v>
       </c>
       <c r="B24" t="n">
-        <v>79708</v>
+        <v>92749</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626247</v>
+        <v>626149</v>
       </c>
       <c r="R24" t="n">
-        <v>6650626</v>
+        <v>6650411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,11 +3136,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774949</v>
+        <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>91431</v>
+        <v>92749</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626135</v>
+        <v>626154</v>
       </c>
       <c r="R25" t="n">
-        <v>6650578</v>
+        <v>6650405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B26" t="n">
-        <v>92748</v>
+        <v>91432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R26" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,37 +2447,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>105682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2485,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R18" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,11 +2530,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>128774958</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>91494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,37 +2568,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626230</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,18 +2630,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2659,10 +2654,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774958</v>
+        <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>91467</v>
+        <v>79735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,34 +2665,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626230</v>
+        <v>626121</v>
       </c>
       <c r="R20" t="n">
-        <v>6650616</v>
+        <v>6650538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,12 +2730,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2756,46 +2760,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B21" t="n">
-        <v>105654</v>
+        <v>79735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R21" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>79708</v>
+        <v>91459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,7 +3063,7 @@
         <v>128774962</v>
       </c>
       <c r="B24" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3160,7 @@
         <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,32 +3254,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>91432</v>
+        <v>79735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1834,48 +1834,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>97490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R12" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,18 +1907,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1940,45 +1931,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B13" t="n">
-        <v>97490</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R13" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,12 +2007,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2037,37 +2037,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B14" t="n">
-        <v>79735</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R14" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,46 +2147,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>79735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R15" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,6 +2221,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2447,46 +2447,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B18" t="n">
-        <v>105682</v>
+        <v>79735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2494,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R18" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,6 +2521,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774958</v>
+        <v>128774954</v>
       </c>
       <c r="B19" t="n">
-        <v>91494</v>
+        <v>79735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,34 +2564,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626230</v>
+        <v>626121</v>
       </c>
       <c r="R19" t="n">
-        <v>6650616</v>
+        <v>6650538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,12 +2629,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2654,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774954</v>
+        <v>128774958</v>
       </c>
       <c r="B20" t="n">
-        <v>79735</v>
+        <v>91494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,37 +2670,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626121</v>
+        <v>626230</v>
       </c>
       <c r="R20" t="n">
-        <v>6650538</v>
+        <v>6650616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,18 +2732,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2760,37 +2756,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>79735</v>
+        <v>105682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774949</v>
+        <v>128774962</v>
       </c>
       <c r="B23" t="n">
-        <v>91459</v>
+        <v>92776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626135</v>
+        <v>626149</v>
       </c>
       <c r="R23" t="n">
-        <v>6650578</v>
+        <v>6650411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,32 +3060,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B24" t="n">
-        <v>92776</v>
+        <v>91459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R24" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B25" t="n">
-        <v>92776</v>
+        <v>79735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R25" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>79735</v>
+        <v>92776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,45 +1834,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>97490</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R12" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,12 +1910,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1931,48 +1940,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>79735</v>
+        <v>97496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R13" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,18 +2013,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2037,46 +2037,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>79739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2084,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R14" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,6 +2111,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,37 +2143,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>79735</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R15" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,11 +2226,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774952</v>
+        <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>79735</v>
+        <v>91499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,37 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626218</v>
+        <v>626230</v>
       </c>
       <c r="R18" t="n">
-        <v>6650628</v>
+        <v>6650616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,18 +2520,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2553,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774958</v>
+        <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>91494</v>
+        <v>79739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,34 +2661,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626230</v>
+        <v>626121</v>
       </c>
       <c r="R20" t="n">
-        <v>6650616</v>
+        <v>6650538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,12 +2726,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774962</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>92776</v>
+        <v>79739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626149</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650411</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,32 +3065,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774949</v>
+        <v>128774962</v>
       </c>
       <c r="B24" t="n">
-        <v>91459</v>
+        <v>92781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626135</v>
+        <v>626149</v>
       </c>
       <c r="R24" t="n">
-        <v>6650578</v>
+        <v>6650411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>79735</v>
+        <v>92781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R25" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3233,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774963</v>
+        <v>128774949</v>
       </c>
       <c r="B26" t="n">
-        <v>92776</v>
+        <v>91464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626154</v>
+        <v>626135</v>
       </c>
       <c r="R26" t="n">
-        <v>6650405</v>
+        <v>6650578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2447,45 +2447,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774958</v>
+        <v>128774968</v>
       </c>
       <c r="B18" t="n">
-        <v>91499</v>
+        <v>105695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626230</v>
+        <v>626195</v>
       </c>
       <c r="R18" t="n">
-        <v>6650616</v>
+        <v>6650509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,6 +2538,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2544,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774952</v>
+        <v>128774958</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2555,37 +2568,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626218</v>
+        <v>626230</v>
       </c>
       <c r="R19" t="n">
-        <v>6650628</v>
+        <v>6650616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2620,18 +2630,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2650,7 +2654,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B20" t="n">
         <v>79739</v>
@@ -2688,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R20" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,46 +2760,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774968</v>
+        <v>128774954</v>
       </c>
       <c r="B21" t="n">
-        <v>105688</v>
+        <v>79739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626195</v>
+        <v>626121</v>
       </c>
       <c r="R21" t="n">
-        <v>6650509</v>
+        <v>6650538</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>91469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,7 +3063,7 @@
         <v>128774962</v>
       </c>
       <c r="B24" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3160,7 @@
         <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,32 +3254,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>91464</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1834,48 +1834,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>97503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R12" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,18 +1907,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1940,45 +1931,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B13" t="n">
-        <v>97503</v>
+        <v>79739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R13" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,12 +2007,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2447,57 +2447,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774968</v>
+        <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>105695</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626195</v>
+        <v>626230</v>
       </c>
       <c r="R18" t="n">
-        <v>6650509</v>
+        <v>6650616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,7 +2526,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2557,45 +2544,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774958</v>
+        <v>128774968</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>105695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626230</v>
+        <v>626195</v>
       </c>
       <c r="R19" t="n">
-        <v>6650616</v>
+        <v>6650509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,6 +2635,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>91469</v>
+        <v>79739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,32 +3065,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B24" t="n">
-        <v>92786</v>
+        <v>91469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R24" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,7 +3162,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774963</v>
+        <v>128774962</v>
       </c>
       <c r="B25" t="n">
         <v>92786</v>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626154</v>
+        <v>626149</v>
       </c>
       <c r="R25" t="n">
-        <v>6650405</v>
+        <v>6650411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>92786</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1834,45 +1834,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>97503</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R12" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,12 +1910,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1931,48 +1940,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>79739</v>
+        <v>97503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R13" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,18 +2013,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2544,46 +2544,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774968</v>
+        <v>128774954</v>
       </c>
       <c r="B19" t="n">
-        <v>105695</v>
+        <v>79739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2591,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626195</v>
+        <v>626121</v>
       </c>
       <c r="R19" t="n">
-        <v>6650509</v>
+        <v>6650538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,6 +2618,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,37 +2756,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774954</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
+        <v>105695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626121</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650538</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>128774962</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>92786</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626149</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,32 +3060,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774949</v>
+        <v>128774963</v>
       </c>
       <c r="B24" t="n">
-        <v>91469</v>
+        <v>92786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626135</v>
+        <v>626154</v>
       </c>
       <c r="R24" t="n">
-        <v>6650578</v>
+        <v>6650405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,32 +3157,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B25" t="n">
-        <v>92786</v>
+        <v>91469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R25" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>92786</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774952</v>
+        <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626218</v>
+        <v>626121</v>
       </c>
       <c r="R20" t="n">
-        <v>6650628</v>
+        <v>6650538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774962</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>92786</v>
+        <v>79743</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626149</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650411</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774963</v>
+        <v>128774962</v>
       </c>
       <c r="B24" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626154</v>
+        <v>626149</v>
       </c>
       <c r="R24" t="n">
-        <v>6650405</v>
+        <v>6650411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774949</v>
+        <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>91469</v>
+        <v>92790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626135</v>
+        <v>626154</v>
       </c>
       <c r="R25" t="n">
-        <v>6650578</v>
+        <v>6650405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>91473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2544,37 +2544,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B19" t="n">
-        <v>79743</v>
+        <v>105699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2582,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R19" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,11 +2627,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,46 +2760,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B21" t="n">
-        <v>105699</v>
+        <v>79743</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R21" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>79743</v>
+        <v>91473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774962</v>
+        <v>128774957</v>
       </c>
       <c r="B24" t="n">
-        <v>92790</v>
+        <v>79743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626149</v>
+        <v>626247</v>
       </c>
       <c r="R24" t="n">
-        <v>6650411</v>
+        <v>6650626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,6 +3131,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,7 +3162,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774963</v>
+        <v>128774962</v>
       </c>
       <c r="B25" t="n">
         <v>92790</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626154</v>
+        <v>626149</v>
       </c>
       <c r="R25" t="n">
-        <v>6650405</v>
+        <v>6650411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>91473</v>
+        <v>92790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1834,48 +1834,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>97507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R12" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,18 +1907,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1940,45 +1931,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B13" t="n">
-        <v>97507</v>
+        <v>79743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R13" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,12 +2007,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2544,46 +2544,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>105699</v>
+        <v>79743</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2591,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,6 +2618,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,37 +2756,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>79743</v>
+        <v>105699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774949</v>
+        <v>128774962</v>
       </c>
       <c r="B23" t="n">
-        <v>91473</v>
+        <v>92790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626135</v>
+        <v>626149</v>
       </c>
       <c r="R23" t="n">
-        <v>6650578</v>
+        <v>6650411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B24" t="n">
-        <v>79743</v>
+        <v>92790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R24" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,11 +3131,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,32 +3157,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B25" t="n">
-        <v>92790</v>
+        <v>91473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R25" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>92790</v>
+        <v>79743</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>128774960</v>
       </c>
       <c r="B12" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>128774953</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,37 +2037,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R14" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,46 +2147,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>79648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R15" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,6 +2221,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>92790</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R23" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B24" t="n">
-        <v>92790</v>
+        <v>79648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R24" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,6 +3131,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774949</v>
+        <v>128774962</v>
       </c>
       <c r="B25" t="n">
-        <v>91473</v>
+        <v>92795</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626135</v>
+        <v>626149</v>
       </c>
       <c r="R25" t="n">
-        <v>6650578</v>
+        <v>6650411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>79743</v>
+        <v>92795</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>92803</v>
+        <v>91485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R23" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774963</v>
+        <v>128774962</v>
       </c>
       <c r="B24" t="n">
         <v>92803</v>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626154</v>
+        <v>626149</v>
       </c>
       <c r="R24" t="n">
-        <v>6650405</v>
+        <v>6650411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>79653</v>
+        <v>92803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R25" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3228,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,32 +3254,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>91485</v>
+        <v>79653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4496,62 +4496,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R37" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4580,7 +4566,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4590,7 +4576,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,48 +4603,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>98651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R38" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1834,48 +1834,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>97527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R12" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,18 +1907,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1940,45 +1931,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B13" t="n">
-        <v>97522</v>
+        <v>79653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R13" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,12 +2007,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774952</v>
+        <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>91523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,37 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626218</v>
+        <v>626230</v>
       </c>
       <c r="R18" t="n">
-        <v>6650628</v>
+        <v>6650616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,18 +2520,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2553,7 +2544,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
         <v>79653</v>
@@ -2591,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,46 +2650,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774968</v>
+        <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>105714</v>
+        <v>79653</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626195</v>
+        <v>626121</v>
       </c>
       <c r="R20" t="n">
-        <v>6650509</v>
+        <v>6650538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,6 +2724,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,45 +2756,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774958</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>105719</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626230</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650616</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,6 +2847,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774949</v>
+        <v>128774962</v>
       </c>
       <c r="B23" t="n">
-        <v>91485</v>
+        <v>92808</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626135</v>
+        <v>626149</v>
       </c>
       <c r="R23" t="n">
-        <v>6650578</v>
+        <v>6650411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774962</v>
+        <v>128774963</v>
       </c>
       <c r="B24" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626149</v>
+        <v>626154</v>
       </c>
       <c r="R24" t="n">
-        <v>6650411</v>
+        <v>6650405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B25" t="n">
-        <v>92803</v>
+        <v>79653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R25" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,6 +3228,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B26" t="n">
-        <v>79653</v>
+        <v>91488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095999</v>
       </c>
       <c r="B35" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095863</v>
       </c>
       <c r="B36" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,45 +1834,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128774960</v>
+        <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>97527</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626202</v>
+        <v>626068</v>
       </c>
       <c r="R12" t="n">
-        <v>6650484</v>
+        <v>6650516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,12 +1910,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1931,48 +1940,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774953</v>
+        <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626068</v>
+        <v>626202</v>
       </c>
       <c r="R13" t="n">
-        <v>6650516</v>
+        <v>6650484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,18 +2013,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,45 +2447,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774958</v>
+        <v>128774968</v>
       </c>
       <c r="B18" t="n">
-        <v>91523</v>
+        <v>105722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626230</v>
+        <v>626195</v>
       </c>
       <c r="R18" t="n">
-        <v>6650616</v>
+        <v>6650509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,6 +2538,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2544,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774952</v>
+        <v>128774958</v>
       </c>
       <c r="B19" t="n">
-        <v>79653</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2555,37 +2568,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626218</v>
+        <v>626230</v>
       </c>
       <c r="R19" t="n">
-        <v>6650628</v>
+        <v>6650616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2620,18 +2630,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2653,7 +2657,7 @@
         <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,46 +2760,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B21" t="n">
-        <v>105719</v>
+        <v>79654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R21" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>128774962</v>
       </c>
       <c r="B23" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>128774963</v>
       </c>
       <c r="B24" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,32 +3157,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B25" t="n">
-        <v>79653</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R25" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,11 +3228,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,32 +3254,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>91488</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095999</v>
       </c>
       <c r="B35" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095863</v>
       </c>
       <c r="B36" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774962</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>92811</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626149</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650411</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3065,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774963</v>
+        <v>128774962</v>
       </c>
       <c r="B24" t="n">
         <v>92811</v>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626154</v>
+        <v>626149</v>
       </c>
       <c r="R24" t="n">
-        <v>6650405</v>
+        <v>6650411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774949</v>
+        <v>128774963</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>92811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626135</v>
+        <v>626154</v>
       </c>
       <c r="R25" t="n">
-        <v>6650578</v>
+        <v>6650405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>91491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2447,57 +2447,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774968</v>
+        <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>105722</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626195</v>
+        <v>626230</v>
       </c>
       <c r="R18" t="n">
-        <v>6650509</v>
+        <v>6650616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,7 +2526,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2557,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774958</v>
+        <v>128774954</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,34 +2555,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626230</v>
+        <v>626121</v>
       </c>
       <c r="R19" t="n">
-        <v>6650616</v>
+        <v>6650538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,12 +2620,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2654,7 +2650,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B20" t="n">
         <v>79654</v>
@@ -2692,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R20" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2760,37 +2756,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>79654</v>
+        <v>105722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>128774962</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>92811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626149</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774962</v>
+        <v>128774963</v>
       </c>
       <c r="B24" t="n">
         <v>92811</v>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626149</v>
+        <v>626154</v>
       </c>
       <c r="R24" t="n">
-        <v>6650411</v>
+        <v>6650405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,32 +3157,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774963</v>
+        <v>128774949</v>
       </c>
       <c r="B25" t="n">
-        <v>92811</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626154</v>
+        <v>626135</v>
       </c>
       <c r="R25" t="n">
-        <v>6650405</v>
+        <v>6650578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,32 +3254,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>91491</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4496,48 +4496,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R37" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4566,7 +4580,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4590,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,62 +4617,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R38" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2544,7 +2544,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
         <v>79654</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774952</v>
+        <v>128774954</v>
       </c>
       <c r="B20" t="n">
         <v>79654</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626218</v>
+        <v>626121</v>
       </c>
       <c r="R20" t="n">
-        <v>6650628</v>
+        <v>6650538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774962</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>92811</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626149</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650411</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,32 +3065,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774963</v>
+        <v>128774949</v>
       </c>
       <c r="B24" t="n">
-        <v>92811</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626154</v>
+        <v>626135</v>
       </c>
       <c r="R24" t="n">
-        <v>6650405</v>
+        <v>6650578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774949</v>
+        <v>128774962</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>92811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626135</v>
+        <v>626149</v>
       </c>
       <c r="R25" t="n">
-        <v>6650578</v>
+        <v>6650411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>92811</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B35" t="n">
         <v>91526</v>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B36" t="n">
         <v>91526</v>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,37 +2037,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R14" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,46 +2147,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>79658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R15" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,6 +2221,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626135</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,32 +3060,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>79658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R24" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,6 +3131,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3165,7 +3165,7 @@
         <v>128774962</v>
       </c>
       <c r="B25" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>129097193</v>
       </c>
       <c r="B27" t="n">
-        <v>57564</v>
+        <v>57566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>129096166</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>129097261</v>
       </c>
       <c r="B40" t="n">
-        <v>56916</v>
+        <v>56918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2037,46 +2037,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2084,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R14" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,6 +2111,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,37 +2143,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>79658</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R15" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,11 +2226,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774952</v>
+        <v>128774954</v>
       </c>
       <c r="B19" t="n">
         <v>79658</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626218</v>
+        <v>626121</v>
       </c>
       <c r="R19" t="n">
-        <v>6650628</v>
+        <v>6650538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B20" t="n">
         <v>79658</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R20" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>92825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R24" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,11 +3131,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3165,7 +3160,7 @@
         <v>128774962</v>
       </c>
       <c r="B25" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B26" t="n">
-        <v>92818</v>
+        <v>79658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3270,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R26" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B35" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B36" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4496,62 +4496,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R37" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4580,7 +4566,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4590,7 +4576,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,48 +4603,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>98676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R38" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128774956</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>128774969</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774952</v>
+        <v>128774954</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626218</v>
+        <v>626121</v>
       </c>
       <c r="R20" t="n">
-        <v>6650628</v>
+        <v>6650538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>128774949</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774963</v>
+        <v>128774957</v>
       </c>
       <c r="B24" t="n">
-        <v>92825</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626154</v>
+        <v>626247</v>
       </c>
       <c r="R24" t="n">
-        <v>6650405</v>
+        <v>6650626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,6 +3131,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3160,7 +3165,7 @@
         <v>128774962</v>
       </c>
       <c r="B25" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3254,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774957</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>92827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626247</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650626</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3359,7 +3359,7 @@
         <v>129097193</v>
       </c>
       <c r="B27" t="n">
-        <v>57566</v>
+        <v>57568</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096280</v>
+        <v>129096398</v>
       </c>
       <c r="B33" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4082,34 +4082,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626236</v>
+        <v>626231</v>
       </c>
       <c r="R33" t="n">
-        <v>6650580</v>
+        <v>6650550</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,7 +4124,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4148,7 +4134,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,10 +4161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129096398</v>
+        <v>129096280</v>
       </c>
       <c r="B34" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4203,20 +4189,34 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626231</v>
+        <v>626236</v>
       </c>
       <c r="R34" t="n">
-        <v>6650550</v>
+        <v>6650580</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,7 +4285,7 @@
         <v>129095999</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095863</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>129097261</v>
       </c>
       <c r="B40" t="n">
-        <v>56918</v>
+        <v>56920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2037,37 +2037,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R14" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,46 +2147,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R15" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,6 +2221,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2544,37 +2544,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B19" t="n">
-        <v>79660</v>
+        <v>105741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2582,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R19" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,11 +2627,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,46 +2760,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B21" t="n">
-        <v>105741</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R21" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774949</v>
+        <v>128774957</v>
       </c>
       <c r="B23" t="n">
-        <v>91506</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626135</v>
+        <v>626247</v>
       </c>
       <c r="R23" t="n">
-        <v>6650578</v>
+        <v>6650626</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774957</v>
+        <v>128774962</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>92827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626247</v>
+        <v>626149</v>
       </c>
       <c r="R24" t="n">
-        <v>6650626</v>
+        <v>6650411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,11 +3136,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,7 +3162,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774962</v>
+        <v>128774963</v>
       </c>
       <c r="B25" t="n">
         <v>92827</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626149</v>
+        <v>626154</v>
       </c>
       <c r="R25" t="n">
-        <v>6650411</v>
+        <v>6650405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774963</v>
+        <v>128774949</v>
       </c>
       <c r="B26" t="n">
-        <v>92827</v>
+        <v>91506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626154</v>
+        <v>626135</v>
       </c>
       <c r="R26" t="n">
-        <v>6650405</v>
+        <v>6650578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096398</v>
+        <v>129096280</v>
       </c>
       <c r="B33" t="n">
         <v>105741</v>
@@ -4082,20 +4082,34 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626231</v>
+        <v>626236</v>
       </c>
       <c r="R33" t="n">
-        <v>6650550</v>
+        <v>6650580</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4124,7 +4138,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4134,7 +4148,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,7 +4175,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129096280</v>
+        <v>129096398</v>
       </c>
       <c r="B34" t="n">
         <v>105741</v>
@@ -4189,34 +4203,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626236</v>
+        <v>626231</v>
       </c>
       <c r="R34" t="n">
-        <v>6650580</v>
+        <v>6650550</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B35" t="n">
         <v>91542</v>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B36" t="n">
         <v>91542</v>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774958</v>
+        <v>128774954</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,34 +2458,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626230</v>
+        <v>626121</v>
       </c>
       <c r="R18" t="n">
-        <v>6650616</v>
+        <v>6650538</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,12 +2523,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2544,46 +2553,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B19" t="n">
-        <v>105741</v>
+        <v>79660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R19" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,6 +2627,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774954</v>
+        <v>128774958</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,37 +2670,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626121</v>
+        <v>626230</v>
       </c>
       <c r="R20" t="n">
-        <v>6650538</v>
+        <v>6650616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,18 +2732,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2760,37 +2756,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774952</v>
+        <v>128774968</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>105741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626218</v>
+        <v>626195</v>
       </c>
       <c r="R21" t="n">
-        <v>6650628</v>
+        <v>6650509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4496,48 +4496,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R37" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4566,7 +4580,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4590,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,62 +4617,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R38" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>128774967</v>
       </c>
       <c r="B8" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128774960</v>
       </c>
       <c r="B13" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,46 +2037,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128774965</v>
+        <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2084,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626206</v>
+        <v>626185</v>
       </c>
       <c r="R14" t="n">
-        <v>6650513</v>
+        <v>6650516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,6 +2111,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,37 +2143,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774955</v>
+        <v>128774965</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626185</v>
+        <v>626206</v>
       </c>
       <c r="R15" t="n">
-        <v>6650516</v>
+        <v>6650513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,11 +2226,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
         <v>128774961</v>
       </c>
       <c r="B16" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774954</v>
+        <v>128774958</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,37 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626121</v>
+        <v>626230</v>
       </c>
       <c r="R18" t="n">
-        <v>6650538</v>
+        <v>6650616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,18 +2520,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2553,7 +2544,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774952</v>
+        <v>128774954</v>
       </c>
       <c r="B19" t="n">
         <v>79660</v>
@@ -2591,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626218</v>
+        <v>626121</v>
       </c>
       <c r="R19" t="n">
-        <v>6650628</v>
+        <v>6650538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,45 +2650,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774958</v>
+        <v>128774968</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>105767</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626230</v>
+        <v>626195</v>
       </c>
       <c r="R20" t="n">
-        <v>6650616</v>
+        <v>6650509</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,6 +2741,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2756,46 +2760,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774968</v>
+        <v>128774952</v>
       </c>
       <c r="B21" t="n">
-        <v>105741</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626195</v>
+        <v>626218</v>
       </c>
       <c r="R21" t="n">
-        <v>6650509</v>
+        <v>6650628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,7 +2869,7 @@
         <v>128774959</v>
       </c>
       <c r="B22" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,32 +3065,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774962</v>
+        <v>128774949</v>
       </c>
       <c r="B24" t="n">
-        <v>92827</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626149</v>
+        <v>626135</v>
       </c>
       <c r="R24" t="n">
-        <v>6650411</v>
+        <v>6650578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774963</v>
+        <v>128774962</v>
       </c>
       <c r="B25" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626154</v>
+        <v>626149</v>
       </c>
       <c r="R25" t="n">
-        <v>6650405</v>
+        <v>6650411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,32 +3259,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774949</v>
+        <v>128774963</v>
       </c>
       <c r="B26" t="n">
-        <v>91506</v>
+        <v>92813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626135</v>
+        <v>626154</v>
       </c>
       <c r="R26" t="n">
-        <v>6650578</v>
+        <v>6650405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,62 +4496,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R37" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4580,7 +4566,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4590,7 +4576,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,48 +4603,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R38" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,10 +3593,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129096466</v>
+        <v>129095727</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3633,22 +3633,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626209</v>
+        <v>626197</v>
       </c>
       <c r="R29" t="n">
-        <v>6650510</v>
+        <v>6650539</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129095727</v>
+        <v>129096466</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626197</v>
+        <v>626209</v>
       </c>
       <c r="R30" t="n">
-        <v>6650539</v>
+        <v>6650510</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,10 +3593,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129095727</v>
+        <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3633,22 +3633,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626197</v>
+        <v>626209</v>
       </c>
       <c r="R29" t="n">
-        <v>6650539</v>
+        <v>6650510</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129096466</v>
+        <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626209</v>
+        <v>626197</v>
       </c>
       <c r="R30" t="n">
-        <v>6650510</v>
+        <v>6650539</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,48 +4496,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R37" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4566,7 +4580,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4590,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,62 +4617,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B38" t="n">
-        <v>98706</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R38" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,62 +4496,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B37" t="n">
-        <v>98710</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R37" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4580,7 +4566,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4590,7 +4576,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,48 +4603,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R38" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096280</v>
+        <v>129096398</v>
       </c>
       <c r="B33" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4082,34 +4082,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626236</v>
+        <v>626231</v>
       </c>
       <c r="R33" t="n">
-        <v>6650580</v>
+        <v>6650550</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,7 +4124,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4148,7 +4134,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,10 +4161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129096398</v>
+        <v>129096280</v>
       </c>
       <c r="B34" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4203,20 +4189,34 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626231</v>
+        <v>626236</v>
       </c>
       <c r="R34" t="n">
-        <v>6650550</v>
+        <v>6650580</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,7 +4285,7 @@
         <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -4054,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096398</v>
+        <v>129096280</v>
       </c>
       <c r="B33" t="n">
         <v>105790</v>
@@ -4082,20 +4082,34 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626231</v>
+        <v>626236</v>
       </c>
       <c r="R33" t="n">
-        <v>6650550</v>
+        <v>6650580</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4124,7 +4138,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4134,7 +4148,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,7 +4175,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129096280</v>
+        <v>129096398</v>
       </c>
       <c r="B34" t="n">
         <v>105790</v>
@@ -4189,34 +4203,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626236</v>
+        <v>626231</v>
       </c>
       <c r="R34" t="n">
-        <v>6650580</v>
+        <v>6650550</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B35" t="n">
         <v>91550</v>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B36" t="n">
         <v>91550</v>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>129096058</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129096466</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>129095727</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129096741</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129096280</v>
       </c>
       <c r="B33" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129096398</v>
       </c>
       <c r="B34" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B35" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B36" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4606,7 @@
         <v>129096166</v>
       </c>
       <c r="B38" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>129096122</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129095625</v>
       </c>
       <c r="B41" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>129096490</v>
       </c>
       <c r="B42" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B35" t="n">
         <v>91553</v>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B36" t="n">
         <v>91553</v>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4496,48 +4496,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096090</v>
+        <v>129096166</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626247</v>
+        <v>626251</v>
       </c>
       <c r="R37" t="n">
-        <v>6650600</v>
+        <v>6650604</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4566,7 +4580,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4590,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,62 +4617,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096166</v>
+        <v>129096090</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626251</v>
+        <v>626247</v>
       </c>
       <c r="R38" t="n">
-        <v>6650604</v>
+        <v>6650600</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095999</v>
+        <v>129095863</v>
       </c>
       <c r="B35" t="n">
         <v>91553</v>
@@ -4313,17 +4313,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626247</v>
+        <v>626231</v>
       </c>
       <c r="R35" t="n">
         <v>6650626</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095863</v>
+        <v>129095999</v>
       </c>
       <c r="B36" t="n">
         <v>91553</v>
@@ -4420,17 +4420,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626231</v>
+        <v>626247</v>
       </c>
       <c r="R36" t="n">
         <v>6650626</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43970-2025 artfynd.xlsx
+++ b/artfynd/A 43970-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55780091</v>
+        <v>128774958</v>
       </c>
       <c r="B2" t="n">
-        <v>5413</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101920</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>tallbestånd V om Mörtsjön (#72), Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626020.7282893497</v>
+        <v>626230</v>
       </c>
       <c r="R2" t="n">
-        <v>6650501.276011564</v>
+        <v>6650616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>inventering ÅGP-insekter på tall</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,84 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>en tallåga med avslutade gnag</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55780092</v>
+        <v>129095863</v>
       </c>
       <c r="B3" t="n">
-        <v>5413</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101920</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>tallbestånd V om Mörtsjön (#72), Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625950.6576074586</v>
+        <v>626231</v>
       </c>
       <c r="R3" t="n">
-        <v>6650510.408277189</v>
+        <v>6650626</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-09-20</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-09-20</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>inventering ÅGP-insekter på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,36 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>tallåga med 1 nytt flyghål</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86831006</v>
+        <v>129095999</v>
       </c>
       <c r="B4" t="n">
-        <v>5207</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,66 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100155</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre timmerman</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acanthocinus griseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjön, 500 m V om, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625940.4442400797</v>
+        <v>626247</v>
       </c>
       <c r="R4" t="n">
-        <v>6650515.57104138</v>
+        <v>6650626</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,27 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På timmerupplag med tall och gran</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,83 +968,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86852718</v>
+        <v>128774962</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626038.1414037416</v>
+        <v>626149</v>
       </c>
       <c r="R5" t="n">
-        <v>6650432.228117764</v>
+        <v>6650411</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,27 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Grabs</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Grabs</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94066907</v>
+        <v>128774963</v>
       </c>
       <c r="B6" t="n">
-        <v>56364</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,38 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100137</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Styggkärret, Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626195.5860978174</v>
+        <v>626154</v>
       </c>
       <c r="R6" t="n">
-        <v>6650260.237653712</v>
+        <v>6650405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,22 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1313,69 +1168,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Pelle Odebrant</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pelle Odebrant</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114783956</v>
+        <v>128774959</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626141</v>
+        <v>626196</v>
       </c>
       <c r="R7" t="n">
-        <v>6650535</v>
+        <v>6650578</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,29 +1259,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Ann Edlund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128774967</v>
+        <v>128774949</v>
       </c>
       <c r="B8" t="n">
-        <v>105767</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626203</v>
+        <v>626135</v>
       </c>
       <c r="R8" t="n">
-        <v>6650513</v>
+        <v>6650578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,7 +1377,7 @@
         <v>128774950</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128774970</v>
+        <v>128774969</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626253</v>
+        <v>626079</v>
       </c>
       <c r="R10" t="n">
-        <v>6650628</v>
+        <v>6650518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128774956</v>
+        <v>128774952</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626194</v>
+        <v>626218</v>
       </c>
       <c r="R11" t="n">
-        <v>6650588</v>
+        <v>6650628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1677,7 @@
         <v>128774953</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,45 +1780,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128774960</v>
+        <v>128774954</v>
       </c>
       <c r="B13" t="n">
-        <v>97575</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626202</v>
+        <v>626121</v>
       </c>
       <c r="R13" t="n">
-        <v>6650484</v>
+        <v>6650538</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,12 +1856,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,7 +1889,7 @@
         <v>128774955</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,46 +1992,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128774965</v>
+        <v>128774956</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626206</v>
+        <v>626194</v>
       </c>
       <c r="R15" t="n">
-        <v>6650513</v>
+        <v>6650588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,6 +2066,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,32 +2098,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128774961</v>
+        <v>128774957</v>
       </c>
       <c r="B16" t="n">
-        <v>97575</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626179</v>
+        <v>626247</v>
       </c>
       <c r="R16" t="n">
-        <v>6650372</v>
+        <v>6650626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,6 +2169,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,45 +2200,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128774969</v>
+        <v>94066907</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>57811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100137</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Styggkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626079</v>
+        <v>626196</v>
       </c>
       <c r="R17" t="n">
-        <v>6650518</v>
+        <v>6650261</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,12 +2269,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,60 +2299,85 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Pelle Odebrant</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Pelle Odebrant</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128774958</v>
+        <v>86830936</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Mörtsjön, 400 m V om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626230</v>
+        <v>626057</v>
       </c>
       <c r="R18" t="n">
-        <v>6650616</v>
+        <v>6650387</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,12 +2401,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På timmerupplag med gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,69 +2420,78 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Rasmus Elleby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128774954</v>
+        <v>86852718</v>
       </c>
       <c r="B19" t="n">
-        <v>79660</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626121</v>
+        <v>626038</v>
       </c>
       <c r="R19" t="n">
-        <v>6650538</v>
+        <v>6650432</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,17 +2515,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-07-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
+          <t>2020-07-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,29 +2539,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Andreas Grabs</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Andreas Grabs</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128774968</v>
+        <v>87264807</v>
       </c>
       <c r="B20" t="n">
-        <v>105767</v>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,46 +2568,55 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Mörtsjön, 400 m V om, Jumkil sn, Upl, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626195</v>
+        <v>626057</v>
       </c>
       <c r="R20" t="n">
-        <v>6650509</v>
+        <v>6650376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,12 +2643,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,57 +2664,54 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hans Elleby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hans Elleby, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128774952</v>
+        <v>128774970</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626218</v>
+        <v>626253</v>
       </c>
       <c r="R21" t="n">
         <v>6650628</v>
@@ -2836,18 +2749,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2866,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128774959</v>
+        <v>129096090</v>
       </c>
       <c r="B22" t="n">
-        <v>92833</v>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,37 +2784,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626196</v>
+        <v>626247</v>
       </c>
       <c r="R22" t="n">
-        <v>6650578</v>
+        <v>6650600</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2931,19 +2838,29 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -2951,60 +2868,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128774957</v>
+        <v>129096310</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626247</v>
+        <v>626246</v>
       </c>
       <c r="R23" t="n">
-        <v>6650626</v>
+        <v>6650580</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3028,24 +2945,29 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3053,57 +2975,67 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128774949</v>
+        <v>55780091</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>5482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>101920</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>tallbestånd V om Mörtsjön (#72), Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626135</v>
+        <v>626021</v>
       </c>
       <c r="R24" t="n">
-        <v>6650578</v>
+        <v>6650501</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,12 +3062,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2015-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2015-09-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>inventering ÅGP-insekter på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,61 +3083,76 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>en tallåga med avslutade gnag</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128774962</v>
+        <v>55780092</v>
       </c>
       <c r="B25" t="n">
-        <v>92813</v>
+        <v>5482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>101920</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>tallbestånd V om Mörtsjön (#72), Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626149</v>
+        <v>625951</v>
       </c>
       <c r="R25" t="n">
-        <v>6650411</v>
+        <v>6650510</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,12 +3179,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2015-09-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2015-09-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>inventering ÅGP-insekter på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,64 +3200,88 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>tallåga med 1 nytt flyghål</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128774963</v>
+        <v>129097261</v>
       </c>
       <c r="B26" t="n">
-        <v>92813</v>
+        <v>57144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mörtsjön, Upl</t>
+          <t>Rastplats Mörtsjön, Vänge-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626154</v>
+        <v>626082</v>
       </c>
       <c r="R26" t="n">
-        <v>6650405</v>
+        <v>6650430</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,12 +3305,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3344,12 +3335,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3359,11 +3350,11 @@
         <v>129097193</v>
       </c>
       <c r="B27" t="n">
-        <v>57568</v>
+        <v>57794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3472,62 +3463,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129096058</v>
+        <v>94066909</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>57785</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102622</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Styggkärret, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626262</v>
+        <v>626196</v>
       </c>
       <c r="R28" t="n">
-        <v>6650614</v>
+        <v>6650261</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3551,22 +3532,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2021-02-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2021-02-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3581,74 +3562,81 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Pelle Odebrant</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Pelle Odebrant</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129096466</v>
+        <v>101494553</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>43464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>201116</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Mörtsjön, 400 m V om, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626209</v>
+        <v>625889</v>
       </c>
       <c r="R29" t="n">
-        <v>6650510</v>
+        <v>6650562</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3672,22 +3660,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,28 +3684,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Kenth Kärsrud, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129095727</v>
+        <v>114783956</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3742,34 +3731,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626197</v>
+        <v>626141</v>
       </c>
       <c r="R30" t="n">
-        <v>6650539</v>
+        <v>6650535</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3793,22 +3772,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,28 +3786,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Carin von Köhler, Ann Edlund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129096741</v>
+        <v>128774965</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,25 +3833,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626173</v>
+        <v>626206</v>
       </c>
       <c r="R31" t="n">
-        <v>6650461</v>
+        <v>6650513</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3905,22 +3882,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,66 +3896,81 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096310</v>
+        <v>129095727</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626246</v>
+        <v>626197</v>
       </c>
       <c r="R32" t="n">
-        <v>6650580</v>
+        <v>6650539</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4017,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4027,14 +4009,14 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4054,37 +4036,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096280</v>
+        <v>129096058</v>
       </c>
       <c r="B33" t="n">
-        <v>105793</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4094,7 +4076,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4103,13 +4085,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626236</v>
+        <v>626262</v>
       </c>
       <c r="R33" t="n">
-        <v>6650580</v>
+        <v>6650614</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,7 +4120,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4148,7 +4130,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,48 +4157,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129096398</v>
+        <v>129096122</v>
       </c>
       <c r="B34" t="n">
-        <v>105793</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626231</v>
+        <v>626253</v>
       </c>
       <c r="R34" t="n">
-        <v>6650550</v>
+        <v>6650595</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,7 +4241,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4251,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,48 +4278,62 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095863</v>
+        <v>129096166</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626231</v>
+        <v>626251</v>
       </c>
       <c r="R35" t="n">
-        <v>6650626</v>
+        <v>6650604</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4352,7 +4362,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4372,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,48 +4399,62 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129095999</v>
+        <v>129096466</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626247</v>
+        <v>626209</v>
       </c>
       <c r="R36" t="n">
-        <v>6650626</v>
+        <v>6650510</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4459,7 +4483,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4493,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4496,10 +4520,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096166</v>
+        <v>129096741</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,16 +4548,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4541,17 +4556,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626251</v>
+        <v>626173</v>
       </c>
       <c r="R37" t="n">
-        <v>6650604</v>
+        <v>6650461</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4580,7 +4595,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4590,7 +4605,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,10 +4632,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096090</v>
+        <v>128774967</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>106243</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,37 +4643,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626247</v>
+        <v>626203</v>
       </c>
       <c r="R38" t="n">
-        <v>6650600</v>
+        <v>6650513</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4682,29 +4697,24 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4712,74 +4722,72 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096122</v>
+        <v>128774968</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>106243</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Upl</t>
+          <t>Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626253</v>
+        <v>626195</v>
       </c>
       <c r="R39" t="n">
-        <v>6650595</v>
+        <v>6650509</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4803,22 +4811,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4827,28 +4825,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129097261</v>
+        <v>129095625</v>
       </c>
       <c r="B40" t="n">
-        <v>56920</v>
+        <v>106243</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,56 +4855,51 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rastplats Mörtsjön, Vänge-Östfora, Upl</t>
+          <t>Hundmossen, Hundmossen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626082</v>
+        <v>626113</v>
       </c>
       <c r="R40" t="n">
-        <v>6650430</v>
+        <v>6650577</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4934,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4944,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4971,10 +4965,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129095625</v>
+        <v>129096280</v>
       </c>
       <c r="B41" t="n">
-        <v>105793</v>
+        <v>106243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5001,32 +4995,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626113</v>
+        <v>626236</v>
       </c>
       <c r="R41" t="n">
-        <v>6650577</v>
+        <v>6650580</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5055,7 +5049,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5065,7 +5059,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5092,10 +5086,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129096490</v>
+        <v>129096398</v>
       </c>
       <c r="B42" t="n">
-        <v>105793</v>
+        <v>106243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,34 +5114,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön, Mörtsjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626197</v>
+        <v>626231</v>
       </c>
       <c r="R42" t="n">
-        <v>6650515</v>
+        <v>6650550</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,7 +5156,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5186,7 +5166,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5210,6 +5190,321 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129096490</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hundmossen, Hundmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626197</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6650515</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128774960</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>626202</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6650484</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128774961</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626179</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6650372</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
